--- a/Infectious disease - FMOH Use Case Prioritization Criteria.xlsx
+++ b/Infectious disease - FMOH Use Case Prioritization Criteria.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Please suggest potential collaborators/institutions</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/DPC</t>
+    <t xml:space="preserve">MoH/DPC</t>
   </si>
   <si>
     <t xml:space="preserve">Infectious Diseases</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">MDR-TB - estimate burden and identify transmission hotspots and risk factors</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Which specific health districts have persistently high numbers of undetected MDR-TB cases?
+    <t xml:space="preserve">1. Which specific health districts have persistently high numbers of undetected MDR-TB cases? 
 2. What factors explain why certain facilities or districts have high levels of undetected MDR-TB cases?</t>
   </si>
   <si>
@@ -84,7 +84,7 @@
 Affects all ages and genders</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH 
+    <t xml:space="preserve">MoH 
 Uog
 HU
 MU
@@ -94,9 +94,7 @@
     <t xml:space="preserve">Malaria - determine drivers of malaria resurgence and estimate impact of control strategies on incidence</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Why is malaria resurgent despite all prevention and control strategies being in place?
-2. How can malaria interventions be effective to control malaria in hotspot areas in Ethiopia?
-3. What is the effect of climate change on malaria transmission dynamics?</t>
+    <t xml:space="preserve">1. Why is malaria resurgent despite prevention and control strategies being in place? 2. How can malaria interventions be effective to control malaria in hotspot areas in Ethiopia? 3. What is the effect of climate change on malaria transmission dynamics in Ethiopia?</t>
   </si>
   <si>
     <t xml:space="preserve">Resurgence of malaria 
@@ -105,7 +103,7 @@
 Lack of understanding on the role of climate change </t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH 
+    <t xml:space="preserve">MoH 
 Uog
 HU
 MU</t>
@@ -115,7 +113,7 @@
   </si>
   <si>
     <t xml:space="preserve">1. Why persistent and recurrent trachoma cases are increasing despite the current implementation of the SAFE strategy?
-2. Does increasing the frequency of Trachoma MDA rounds help reduce the prevalence of Trachoma Folliculitis?
+2. Does increasing the frequency of trachoma MDA rounds help reduce the prevalence of trachoma folliculitis?
 3. How significantly do current WASH interventions contribute to breaking the cycle of infection and promoting the long-term health and well-being of communities?</t>
   </si>
   <si>
@@ -125,7 +123,7 @@
 Blindless lifelong problem</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH 
+    <t xml:space="preserve">MoH 
 Uog
 HU
 MU
@@ -136,7 +134,7 @@
 Amarf</t>
   </si>
   <si>
-    <t xml:space="preserve">FmoH/UOG</t>
+    <t xml:space="preserve">MoH/UOG</t>
   </si>
   <si>
     <t xml:space="preserve">Measles - analyse outbreak patterns and identify immunisation gaps driving transmission</t>
@@ -145,14 +143,14 @@
     <t xml:space="preserve">1. What factors drive measles outbreak despite high vaccination coverage in Ethiopia?
 2. How do climate variability and seasonal patterns influence measles outbreaks?
 3. What is the effectiveness of targeted vaccination strategies?
-4. How can Ethiopia prioritize limited vaccine resources for maximum impact?</t>
+4. How can Ethiopia prioritise limited vaccine resources for maximum impact?</t>
   </si>
   <si>
     <t xml:space="preserve">Recurrent outbreaks 
 High morbidity and mortality, especially among child, lactating women and pregnant women</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH 
+    <t xml:space="preserve">MoH 
 Uog
 HU
 MU
@@ -168,7 +166,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +234,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -312,7 +316,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -353,15 +357,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -369,15 +373,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -828,7 +836,7 @@
       <c r="C5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="11" t="n">
@@ -874,149 +882,149 @@
       <c r="AA5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D11" s="7"/>
